--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9931-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9931-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D9A75A-A7A5-4A00-9756-C79DF728DA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6128E45-E89E-4CED-8774-5B451C54A300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F42CE8F1-6696-4A3B-93BB-27960609DA0A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A7BD81CA-BEC0-4A84-8401-2C49134E3A49}"/>
   </bookViews>
   <sheets>
     <sheet name="9931-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1580,29 +1580,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BE7C5E-062E-4875-A166-53CC39EC61E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33B47DC-93DB-4857-921C-464F5A50E4E0}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1635,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1671,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1724,7 +1723,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1792,7 +1791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2022</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="43"/>
       <c r="B8" s="44"/>
       <c r="C8" s="18" t="s">
@@ -2036,7 +2035,7 @@
       <c r="W8" s="50"/>
       <c r="X8" s="46"/>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2021</v>
       </c>
@@ -2108,7 +2107,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>2019</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="53"/>
       <c r="B12" s="54"/>
       <c r="C12" s="20" t="s">
@@ -2280,7 +2279,7 @@
       <c r="W12" s="60"/>
       <c r="X12" s="56"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2018</v>
       </c>
@@ -2352,7 +2351,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2017</v>
       </c>
@@ -2424,7 +2423,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2016</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2015</v>
       </c>
@@ -2568,7 +2567,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2014</v>
       </c>
@@ -2640,7 +2639,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>2013</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
       <c r="C19" s="20" t="s">
@@ -2740,7 +2739,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="56"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2012</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2011</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2010</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2009</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2008</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2007</v>
       </c>
@@ -3172,7 +3171,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2006</v>
       </c>
@@ -3244,7 +3243,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2005</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2004</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2003</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2002</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2001</v>
       </c>
@@ -3604,7 +3603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2000</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1999</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1998</v>
       </c>
@@ -3820,7 +3819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>1997</v>
       </c>
@@ -3892,7 +3891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53"/>
       <c r="B36" s="54"/>
       <c r="C36" s="20" t="s">
@@ -3920,7 +3919,7 @@
       <c r="W36" s="60"/>
       <c r="X36" s="56"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1996</v>
       </c>
@@ -3992,7 +3991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1995</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1994</v>
       </c>
@@ -4136,7 +4135,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1993</v>
       </c>
@@ -4208,7 +4207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1992</v>
       </c>
@@ -4280,7 +4279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39" t="s">
         <v>62</v>
       </c>
